--- a/artfynd/A 50895-2024 artfynd.xlsx
+++ b/artfynd/A 50895-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121090594</v>
       </c>
       <c r="B2" t="n">
-        <v>78598</v>
+        <v>78601</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>121090766</v>
       </c>
       <c r="B3" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 50895-2024 artfynd.xlsx
+++ b/artfynd/A 50895-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121090594</v>
+        <v>121090766</v>
       </c>
       <c r="B2" t="n">
-        <v>78601</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488205</v>
+        <v>488268</v>
       </c>
       <c r="R2" t="n">
-        <v>7006559</v>
+        <v>7006493</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121090766</v>
+        <v>121090594</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>78601</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488268</v>
+        <v>488205</v>
       </c>
       <c r="R3" t="n">
-        <v>7006493</v>
+        <v>7006559</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 50895-2024 artfynd.xlsx
+++ b/artfynd/A 50895-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121090766</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>121090594</v>
       </c>
       <c r="B3" t="n">
-        <v>78601</v>
+        <v>78604</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 50895-2024 artfynd.xlsx
+++ b/artfynd/A 50895-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121090766</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 50895-2024 artfynd.xlsx
+++ b/artfynd/A 50895-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121090766</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>121090594</v>
       </c>
       <c r="B3" t="n">
-        <v>78604</v>
+        <v>78607</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>

--- a/artfynd/A 50895-2024 artfynd.xlsx
+++ b/artfynd/A 50895-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,108 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128546300</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57685</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gräfsåsen vnv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>488335</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7006387</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 50895-2024 artfynd.xlsx
+++ b/artfynd/A 50895-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128546300</v>
       </c>
       <c r="B4" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50895-2024 artfynd.xlsx
+++ b/artfynd/A 50895-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128546300</v>
       </c>
       <c r="B4" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50895-2024 artfynd.xlsx
+++ b/artfynd/A 50895-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128546300</v>
       </c>
       <c r="B4" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50895-2024 artfynd.xlsx
+++ b/artfynd/A 50895-2024 artfynd.xlsx
@@ -902,7 +902,7 @@
         <v>128546300</v>
       </c>
       <c r="B4" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 50895-2024 artfynd.xlsx
+++ b/artfynd/A 50895-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121090766</v>
+        <v>104404176</v>
       </c>
       <c r="B2" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gräfsåsen, Gräfsåsen, Jmt</t>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488268</v>
+        <v>487530</v>
       </c>
       <c r="R2" t="n">
-        <v>7006493</v>
+        <v>7006325</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +744,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>10:08</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>10:08</t>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,62 +769,66 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121090594</v>
+        <v>104403095</v>
       </c>
       <c r="B3" t="n">
-        <v>78607</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gräfsåsen, Gräfsåsen, Jmt</t>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488205</v>
+        <v>487051</v>
       </c>
       <c r="R3" t="n">
-        <v>7006559</v>
+        <v>7006181</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +855,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:58</t>
+          <t>2022-06-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,57 +880,66 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Väg och Miljö AB</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Sonnvik</t>
+          <t>Väg och Miljö AB, Klas Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128546300</v>
+        <v>104403097</v>
       </c>
       <c r="B4" t="n">
-        <v>57723</v>
+        <v>99140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gräfsåsen vnv, Jmt</t>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488335</v>
+        <v>487172</v>
       </c>
       <c r="R4" t="n">
-        <v>7006387</v>
+        <v>7006325</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,17 +966,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-09-19</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,15 +991,3199 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>104404395</v>
+      </c>
+      <c r="B5" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>487995</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7006326</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121090594</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gräfsåsen, Gräfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>488205</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7006559</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121090755</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gräfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>488267</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7006510</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128546300</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gräfsåsen vnv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>488335</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7006387</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128546301</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gräfsåsen vnv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>488342</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7006462</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128546302</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gräfsåsen vnv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>488322</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7006496</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128546304</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gräfsåsen vnv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>488301</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7006508</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128546305</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gräfsåsen vnv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>488290</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7006510</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128546306</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gräfsåsen vnv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>488277</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7006519</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128546307</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gräfsåsen vnv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>488274</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7006525</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128546308</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gräfsåsen vnv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>488268</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7006523</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128546310</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gräfsåsen vnv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>488263</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7006528</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128546311</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gräfsåsen vnv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>488258</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7006538</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128546312</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gräfsåsen vnv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>488253</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7006537</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128546313</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gräfsåsen vnv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>488250</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7006540</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128546314</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Gräfsåsen vnv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>488250</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7006543</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128546315</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Gräfsåsen vnv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>488246</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7006547</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128546316</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Gräfsåsen vnv, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>488226</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7006551</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-09-19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>104403573</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>488041</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7006249</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>104403580</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99456</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219880</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Kransrams</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Polygonatum verticillatum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) All.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>487720</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7006420</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121090599</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Gräfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>488217</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7006553</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>100 +</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anne Siivola</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>121090766</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Gräfsåsen, Gräfsåsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>488268</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7006493</v>
+      </c>
+      <c r="S26" t="n">
+        <v>5</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-11-09</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Per Sonnvik</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>104403004</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>488285</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7006898</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Klas Andersson, Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>104403007</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>488284</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7006896</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-08-24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Klas Andersson, Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>104403021</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>488341</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7006734</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Klas Andersson, Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>104402956</v>
+      </c>
+      <c r="B30" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>487811</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7006431</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Klas Andersson, Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>104403938</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>488088</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7006721</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>104403946</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>488001</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7006324</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>104403953</v>
+      </c>
+      <c r="B33" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>487775</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7006429</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>104403956</v>
+      </c>
+      <c r="B34" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>FURULUND GRÄFSÅSEN, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>487740</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7006435</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-08-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering FURULUND GRÄFSÅSEN för Östersunds kommun.</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Väg och Miljö AB, Klas Andersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50895-2024 artfynd.xlsx
+++ b/artfynd/A 50895-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104403095</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104403097</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1000,6 +1015,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104404395</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,6 +1127,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121090594</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,6 +1238,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104404176</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1320,6 +1350,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121090755</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1422,6 +1457,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546300</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1524,6 +1564,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546301</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,6 +1671,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546302</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1728,6 +1778,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546304</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1830,6 +1885,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546305</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1932,6 +1992,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546306</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2034,6 +2099,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546307</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2136,6 +2206,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546308</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2238,6 +2313,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546310</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2340,6 +2420,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546311</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2442,6 +2527,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546312</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2544,6 +2634,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546313</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2646,6 +2741,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546314</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2748,6 +2848,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546315</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2850,6 +2955,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128546316</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2961,6 +3071,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104403573</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3072,6 +3187,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104403580</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3189,6 +3309,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121090599</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3296,6 +3421,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121090766</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3407,6 +3537,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104403004</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3518,6 +3653,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104403007</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3629,6 +3769,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104403021</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3740,6 +3885,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104402956</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3851,6 +4001,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104403938</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3962,6 +4117,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104403946</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4073,6 +4233,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104403953</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4184,8 +4349,48 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104403956</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>